--- a/九龙-启德-维港．湾畔第2B期/维港．湾畔第2B期_销控明细表.xlsx
+++ b/九龙-启德-维港．湾畔第2B期/维港．湾畔第2B期_销控明细表.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -125,6 +125,12 @@
       <color rgb="00660000"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -202,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -268,6 +274,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -21764,7 +21773,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="H303" s="5" t="n">
@@ -22390,7 +22399,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H312" s="5" t="n">
@@ -24906,7 +24915,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H348" s="5" t="n">
@@ -24972,7 +24981,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H349" s="5" t="n">
@@ -25528,7 +25537,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="H357" s="5" t="n">
@@ -25594,7 +25603,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H358" s="5" t="n">
@@ -26150,7 +26159,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="H366" s="5" t="n">
@@ -26216,7 +26225,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H367" s="5" t="n">
@@ -26772,7 +26781,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H375" s="5" t="n">
@@ -26838,7 +26847,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H376" s="5" t="n">
@@ -27464,7 +27473,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H385" s="5" t="n">
@@ -28090,7 +28099,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H394" s="5" t="n">
@@ -28646,7 +28655,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H402" s="5" t="n">
@@ -28712,7 +28721,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H403" s="5" t="n">
@@ -29268,7 +29277,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H411" s="5" t="n">
@@ -29334,7 +29343,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H412" s="5" t="n">
@@ -30520,7 +30529,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H429" s="5" t="n">
@@ -30586,7 +30595,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H430" s="5" t="n">
@@ -30997,7 +31006,7 @@
       </c>
       <c r="F436" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G436" s="3" t="inlineStr">
@@ -31007,12 +31016,12 @@
       </c>
       <c r="H436" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I436" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J436" s="3" t="inlineStr">
@@ -31022,12 +31031,12 @@
       </c>
       <c r="K436" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L436" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M436" s="3" t="inlineStr">
@@ -31037,7 +31046,7 @@
       </c>
       <c r="N436" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -31142,7 +31151,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H438" s="5" t="n">
@@ -31208,7 +31217,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H439" s="5" t="n">
@@ -31619,7 +31628,7 @@
       </c>
       <c r="F445" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G445" s="3" t="inlineStr">
@@ -31629,12 +31638,12 @@
       </c>
       <c r="H445" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I445" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J445" s="3" t="inlineStr">
@@ -31644,12 +31653,12 @@
       </c>
       <c r="K445" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L445" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M445" s="3" t="inlineStr">
@@ -31659,7 +31668,7 @@
       </c>
       <c r="N445" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -31764,7 +31773,7 @@
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H447" s="5" t="n">
@@ -31830,7 +31839,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H448" s="5" t="n">
@@ -32386,7 +32395,7 @@
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H456" s="5" t="n">
@@ -32452,7 +32461,7 @@
       </c>
       <c r="G457" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H457" s="5" t="n">
@@ -33008,7 +33017,7 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H465" s="5" t="n">
@@ -33074,7 +33083,7 @@
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="H466" s="5" t="n">
@@ -33485,7 +33494,7 @@
       </c>
       <c r="F472" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G472" s="3" t="inlineStr">
@@ -33495,12 +33504,12 @@
       </c>
       <c r="H472" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I472" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J472" s="3" t="inlineStr">
@@ -33510,12 +33519,12 @@
       </c>
       <c r="K472" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L472" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M472" s="3" t="inlineStr">
@@ -33525,7 +33534,7 @@
       </c>
       <c r="N472" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -33630,7 +33639,7 @@
       </c>
       <c r="G474" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H474" s="5" t="n">
@@ -33696,7 +33705,7 @@
       </c>
       <c r="G475" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H475" s="5" t="n">
@@ -34107,7 +34116,7 @@
       </c>
       <c r="F481" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G481" s="3" t="inlineStr">
@@ -34117,12 +34126,12 @@
       </c>
       <c r="H481" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I481" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J481" s="3" t="inlineStr">
@@ -34132,12 +34141,12 @@
       </c>
       <c r="K481" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L481" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M481" s="3" t="inlineStr">
@@ -34147,7 +34156,7 @@
       </c>
       <c r="N481" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -34252,7 +34261,7 @@
       </c>
       <c r="G483" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H483" s="5" t="n">
@@ -34318,7 +34327,7 @@
       </c>
       <c r="G484" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H484" s="5" t="n">
@@ -34874,7 +34883,7 @@
       </c>
       <c r="G492" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H492" s="5" t="n">
@@ -34940,7 +34949,7 @@
       </c>
       <c r="G493" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H493" s="5" t="n">
@@ -35496,7 +35505,7 @@
       </c>
       <c r="G501" s="3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="H501" s="5" t="n">
@@ -35562,7 +35571,7 @@
       </c>
       <c r="G502" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H502" s="5" t="n">
@@ -36118,7 +36127,7 @@
       </c>
       <c r="G510" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H510" s="5" t="n">
@@ -36184,7 +36193,7 @@
       </c>
       <c r="G511" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H511" s="5" t="n">
@@ -38804,27 +38813,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>199</t>
         </is>
       </c>
     </row>
@@ -39108,7 +39117,7 @@
           <t>B | 667呎 (3房)
 $2576万
 $38,622/呎
-(26年-07月-16日)</t>
+(26年-07月-17日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -39187,7 +39196,7 @@
           <t>B | 667呎 (3房)
 $2551万
 $38,240/呎
-(26年-06月-28日)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -39495,7 +39504,7 @@
           <t>A | 744呎 (3房)
 $3211万
 $43,163/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -39503,7 +39512,7 @@
           <t>B | 667呎 (3房)
 $2463万
 $36,930/呎
-(26年-07月-08日)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -39574,7 +39583,7 @@
           <t>A | 744呎 (3房)
 $2663万
 $35,792/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -39582,7 +39591,7 @@
           <t>B | 667呎 (3房)
 $2236万
 $33,522/呎
-(26年-05月-03日)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -39653,7 +39662,7 @@
           <t>A | 744呎 (3房)
 $2575万
 $34,614/呎
-(26年-04月-20日)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -39661,7 +39670,7 @@
           <t>B | 667呎 (3房)
 $2225万
 $33,357/呎
-(26年-05月-04日)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -39732,7 +39741,7 @@
           <t>A | 744呎 (3房)
 $3069万
 $41,246/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -39740,7 +39749,7 @@
           <t>B | 667呎 (3房)
 $2342万
 $35,105/呎
-(26年-06月-08日)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -39811,7 +39820,7 @@
           <t>A | 744呎 (3房)
 $3094万
 $41,586/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -39890,7 +39899,7 @@
           <t>A | 744呎 (3房)
 $3080万
 $41,403/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -39969,7 +39978,7 @@
           <t>A | 744呎 (3房)
 $2524万
 $33,929/呎
-(26年-04月-29日)</t>
+(26年-04月-30日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -39977,7 +39986,7 @@
           <t>B | 667呎 (3房)
 $2181万
 $32,697/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -40048,7 +40057,7 @@
           <t>A | 744呎 (3房)
 $2512万
 $33,761/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -40056,7 +40065,7 @@
           <t>B | 667呎 (3房)
 $2295万
 $34,411/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -40206,7 +40215,7 @@
           <t>A | 744呎 (3房)
 $2985万
 $40,126/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -40214,7 +40223,7 @@
           <t>B | 667呎 (3房)
 $2220万
 $33,279/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -40285,7 +40294,7 @@
           <t>A | 744呎 (3房)
 $2462万
 $33,089/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -40293,7 +40302,7 @@
           <t>B | 667呎 (3房)
 $2127万
 $31,885/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -40304,12 +40313,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E23" s="20" t="inlineStr">
+      <c r="E23" s="23" t="inlineStr">
         <is>
           <t>D | 662呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -40364,7 +40373,7 @@
           <t>A | 744呎 (3房)
 $2450万
 $32,925/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -40372,7 +40381,7 @@
           <t>B | 667呎 (3房)
 $2116万
 $31,726/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -40383,12 +40392,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E24" s="20" t="inlineStr">
+      <c r="E24" s="23" t="inlineStr">
         <is>
           <t>D | 662呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -40443,7 +40452,7 @@
           <t>A | 744呎 (3房)
 $2437万
 $32,759/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -40451,7 +40460,7 @@
           <t>B | 667呎 (3房)
 $2106万
 $31,567/呎
-(26年-04月-29日)</t>
+(26年-04月-30日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -40522,7 +40531,7 @@
           <t>A | 744呎 (3房)
 $2425万
 $32,595/呎
-(26年-05月-03日)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -40530,7 +40539,7 @@
           <t>B | 667呎 (3房)
 $2135万
 $32,013/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -40601,7 +40610,7 @@
           <t>A | 744呎 (3房)
 $2413万
 $32,433/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -40609,7 +40618,7 @@
           <t>B | 667呎 (3房)
 $2245万
 $33,657/呎
-(26年-06月-10日)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -40620,12 +40629,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E27" s="20" t="inlineStr">
+      <c r="E27" s="23" t="inlineStr">
         <is>
           <t>D | 662呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -40680,7 +40689,7 @@
           <t>A | 744呎 (3房)
 $2401万
 $32,270/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -40688,7 +40697,7 @@
           <t>B | 667呎 (3房)
 $2212万
 $33,156/呎
-(26年-06月-11日)</t>
+(26年-06月-12日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -40699,12 +40708,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E28" s="20" t="inlineStr">
+      <c r="E28" s="23" t="inlineStr">
         <is>
           <t>D | 662呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -40759,7 +40768,7 @@
           <t>A | 744呎 (3房)
 $2388万
 $32,091/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -40767,7 +40776,7 @@
           <t>B | 667呎 (3房)
 $2195万
 $32,909/呎
-(26年-07月-15日)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -40838,7 +40847,7 @@
           <t>A | 744呎 (3房)
 $2364万
 $31,770/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="C30" s="22" t="inlineStr">
@@ -40846,7 +40855,7 @@
           <t>B | 667呎 (3房)
 $2151万
 $32,252/呎
-(26年-07月-20日)</t>
+(26年-07月-21日)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -40917,7 +40926,7 @@
           <t>A | 744呎 (3房)
 $2306万
 $30,996/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="C31" s="22" t="inlineStr">
@@ -40925,7 +40934,7 @@
           <t>B | 667呎 (3房)
 $1951万
 $29,244/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">

--- a/九龙-启德-维港．湾畔第2B期/维港．湾畔第2B期_销控明细表.xlsx
+++ b/九龙-启德-维港．湾畔第2B期/维港．湾畔第2B期_销控明细表.xlsx
@@ -31628,23 +31628,19 @@
       </c>
       <c r="F445" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H445" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I445" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="H445" s="5" t="n">
+        <v>19093000</v>
+      </c>
+      <c r="I445" s="5" t="n">
+        <v>28841</v>
       </c>
       <c r="J445" s="3" t="inlineStr">
         <is>
@@ -31653,12 +31649,12 @@
       </c>
       <c r="K445" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L445" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M445" s="3" t="inlineStr">
@@ -31668,7 +31664,7 @@
       </c>
       <c r="N445" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -38813,7 +38809,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -38823,7 +38819,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -40392,12 +40388,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E24" s="23" t="inlineStr">
+      <c r="E24" s="22" t="inlineStr">
         <is>
           <t>D | 662呎 (3房)
-招标单位
--
-(在售)</t>
+$1909万
+$28,841/呎
+(26年-07月-31日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">

--- a/九龙-启德-维港．湾畔第2B期/维港．湾畔第2B期_销控明细表.xlsx
+++ b/九龙-启德-维港．湾畔第2B期/维港．湾畔第2B期_销控明细表.xlsx
@@ -24280,7 +24280,7 @@
       </c>
       <c r="F339" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G339" s="3" t="inlineStr">
@@ -24290,12 +24290,12 @@
       </c>
       <c r="H339" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I339" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J339" s="3" t="inlineStr">
@@ -24305,12 +24305,12 @@
       </c>
       <c r="K339" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L339" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M339" s="3" t="inlineStr">
@@ -24320,7 +24320,7 @@
       </c>
       <c r="N339" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -24350,7 +24350,7 @@
       </c>
       <c r="F340" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G340" s="3" t="inlineStr">
@@ -24360,12 +24360,12 @@
       </c>
       <c r="H340" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I340" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J340" s="3" t="inlineStr">
@@ -24375,12 +24375,12 @@
       </c>
       <c r="K340" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L340" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M340" s="3" t="inlineStr">
@@ -24390,7 +24390,7 @@
       </c>
       <c r="N340" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -27398,7 +27398,7 @@
       </c>
       <c r="F384" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G384" s="3" t="inlineStr">
@@ -27408,12 +27408,12 @@
       </c>
       <c r="H384" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I384" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J384" s="3" t="inlineStr">
@@ -27423,12 +27423,12 @@
       </c>
       <c r="K384" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L384" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M384" s="3" t="inlineStr">
@@ -27438,7 +27438,7 @@
       </c>
       <c r="N384" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -28024,7 +28024,7 @@
       </c>
       <c r="F393" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G393" s="3" t="inlineStr">
@@ -28034,12 +28034,12 @@
       </c>
       <c r="H393" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I393" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J393" s="3" t="inlineStr">
@@ -28049,12 +28049,12 @@
       </c>
       <c r="K393" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L393" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M393" s="3" t="inlineStr">
@@ -28064,7 +28064,7 @@
       </c>
       <c r="N393" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -38809,7 +38809,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -38829,7 +38829,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>195</t>
         </is>
       </c>
     </row>
@@ -39416,20 +39416,20 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>A | 744呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -39819,12 +39819,12 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="C17" s="20" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -39898,12 +39898,12 @@
 (26年-06月-01日)</t>
         </is>
       </c>
-      <c r="C18" s="20" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">

--- a/九龙-启德-维港．湾畔第2B期/维港．湾畔第2B期_销控明细表.xlsx
+++ b/九龙-启德-维港．湾畔第2B期/维港．湾畔第2B期_销控明细表.xlsx
@@ -122,13 +122,13 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
+      <color rgb="00660000"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -273,10 +273,10 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -20508,7 +20508,7 @@
       </c>
       <c r="F285" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G285" s="3" t="inlineStr">
@@ -20518,12 +20518,12 @@
       </c>
       <c r="H285" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I285" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J285" s="3" t="inlineStr">
@@ -20533,12 +20533,12 @@
       </c>
       <c r="K285" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L285" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M285" s="3" t="inlineStr">
@@ -20548,7 +20548,7 @@
       </c>
       <c r="N285" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -21138,7 +21138,7 @@
       </c>
       <c r="F294" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G294" s="3" t="inlineStr">
@@ -21148,12 +21148,12 @@
       </c>
       <c r="H294" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I294" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J294" s="3" t="inlineStr">
@@ -21163,12 +21163,12 @@
       </c>
       <c r="K294" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L294" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M294" s="3" t="inlineStr">
@@ -21178,7 +21178,7 @@
       </c>
       <c r="N294" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -23020,7 +23020,7 @@
       </c>
       <c r="F321" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G321" s="3" t="inlineStr">
@@ -23030,12 +23030,12 @@
       </c>
       <c r="H321" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I321" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J321" s="3" t="inlineStr">
@@ -23045,12 +23045,12 @@
       </c>
       <c r="K321" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L321" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M321" s="3" t="inlineStr">
@@ -23060,7 +23060,7 @@
       </c>
       <c r="N321" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -23650,7 +23650,7 @@
       </c>
       <c r="F330" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G330" s="3" t="inlineStr">
@@ -23660,12 +23660,12 @@
       </c>
       <c r="H330" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I330" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J330" s="3" t="inlineStr">
@@ -23675,12 +23675,12 @@
       </c>
       <c r="K330" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L330" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M330" s="3" t="inlineStr">
@@ -23690,7 +23690,7 @@
       </c>
       <c r="N330" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -38809,7 +38809,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -38829,7 +38829,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>191</t>
         </is>
       </c>
     </row>
@@ -38950,12 +38950,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -39029,12 +39029,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -39108,7 +39108,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
 $2576万
@@ -39187,7 +39187,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
 $2551万
@@ -39266,12 +39266,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -39345,12 +39345,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -39416,7 +39416,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>A | 744呎 (3房)
 招标单位
@@ -39424,7 +39424,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
 招标单位
@@ -39495,7 +39495,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>A | 744呎 (3房)
 $3211万
@@ -39503,7 +39503,7 @@
 (26年-05月-18日)</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
 $2463万
@@ -39574,7 +39574,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>A | 744呎 (3房)
 $2663万
@@ -39582,7 +39582,7 @@
 (26年-04月-23日)</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
 $2236万
@@ -39653,7 +39653,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>A | 744呎 (3房)
 $2575万
@@ -39661,7 +39661,7 @@
 (26年-04月-21日)</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
 $2225万
@@ -39732,7 +39732,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t>A | 744呎 (3房)
 $3069万
@@ -39740,7 +39740,7 @@
 (26年-05月-19日)</t>
         </is>
       </c>
-      <c r="C16" s="22" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
 $2342万
@@ -39811,7 +39811,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>A | 744呎 (3房)
 $3094万
@@ -39819,7 +39819,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
 招标单位
@@ -39890,7 +39890,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>A | 744呎 (3房)
 $3080万
@@ -39898,7 +39898,7 @@
 (26年-06月-01日)</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
 招标单位
@@ -39969,7 +39969,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B19" s="22" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>A | 744呎 (3房)
 $2524万
@@ -39977,7 +39977,7 @@
 (26年-04月-30日)</t>
         </is>
       </c>
-      <c r="C19" s="22" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
 $2181万
@@ -40048,7 +40048,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B20" s="22" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>A | 744呎 (3房)
 $2512万
@@ -40056,7 +40056,7 @@
 (26年-04月-23日)</t>
         </is>
       </c>
-      <c r="C20" s="22" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
 $2295万
@@ -40206,7 +40206,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B22" s="22" t="inlineStr">
+      <c r="B22" s="23" t="inlineStr">
         <is>
           <t>A | 744呎 (3房)
 $2985万
@@ -40214,7 +40214,7 @@
 (26年-05月-11日)</t>
         </is>
       </c>
-      <c r="C22" s="22" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
 $2220万
@@ -40285,7 +40285,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="23" t="inlineStr">
         <is>
           <t>A | 744呎 (3房)
 $2462万
@@ -40293,7 +40293,7 @@
 (26年-04月-22日)</t>
         </is>
       </c>
-      <c r="C23" s="22" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
 $2127万
@@ -40309,7 +40309,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E23" s="23" t="inlineStr">
+      <c r="E23" s="22" t="inlineStr">
         <is>
           <t>D | 662呎 (3房)
 招标单位
@@ -40364,7 +40364,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="23" t="inlineStr">
         <is>
           <t>A | 744呎 (3房)
 $2450万
@@ -40372,7 +40372,7 @@
 (26年-05月-08日)</t>
         </is>
       </c>
-      <c r="C24" s="22" t="inlineStr">
+      <c r="C24" s="23" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
 $2116万
@@ -40388,7 +40388,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E24" s="22" t="inlineStr">
+      <c r="E24" s="23" t="inlineStr">
         <is>
           <t>D | 662呎 (3房)
 $1909万
@@ -40443,7 +40443,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B25" s="23" t="inlineStr">
         <is>
           <t>A | 744呎 (3房)
 $2437万
@@ -40451,7 +40451,7 @@
 (26年-04月-27日)</t>
         </is>
       </c>
-      <c r="C25" s="22" t="inlineStr">
+      <c r="C25" s="23" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
 $2106万
@@ -40522,7 +40522,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B26" s="22" t="inlineStr">
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>A | 744呎 (3房)
 $2425万
@@ -40530,7 +40530,7 @@
 (26年-05月-04日)</t>
         </is>
       </c>
-      <c r="C26" s="22" t="inlineStr">
+      <c r="C26" s="23" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
 $2135万
@@ -40601,7 +40601,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B27" s="22" t="inlineStr">
+      <c r="B27" s="23" t="inlineStr">
         <is>
           <t>A | 744呎 (3房)
 $2413万
@@ -40609,7 +40609,7 @@
 (26年-04月-27日)</t>
         </is>
       </c>
-      <c r="C27" s="22" t="inlineStr">
+      <c r="C27" s="23" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
 $2245万
@@ -40625,7 +40625,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E27" s="23" t="inlineStr">
+      <c r="E27" s="22" t="inlineStr">
         <is>
           <t>D | 662呎 (3房)
 招标单位
@@ -40680,7 +40680,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B28" s="22" t="inlineStr">
+      <c r="B28" s="23" t="inlineStr">
         <is>
           <t>A | 744呎 (3房)
 $2401万
@@ -40688,7 +40688,7 @@
 (26年-04月-24日)</t>
         </is>
       </c>
-      <c r="C28" s="22" t="inlineStr">
+      <c r="C28" s="23" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
 $2212万
@@ -40704,7 +40704,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E28" s="23" t="inlineStr">
+      <c r="E28" s="22" t="inlineStr">
         <is>
           <t>D | 662呎 (3房)
 招标单位
@@ -40759,7 +40759,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B29" s="22" t="inlineStr">
+      <c r="B29" s="23" t="inlineStr">
         <is>
           <t>A | 744呎 (3房)
 $2388万
@@ -40767,7 +40767,7 @@
 (26年-04月-22日)</t>
         </is>
       </c>
-      <c r="C29" s="22" t="inlineStr">
+      <c r="C29" s="23" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
 $2195万
@@ -40838,7 +40838,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B30" s="22" t="inlineStr">
+      <c r="B30" s="23" t="inlineStr">
         <is>
           <t>A | 744呎 (3房)
 $2364万
@@ -40846,7 +40846,7 @@
 (26年-05月-08日)</t>
         </is>
       </c>
-      <c r="C30" s="22" t="inlineStr">
+      <c r="C30" s="23" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
 $2151万
@@ -40917,7 +40917,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B31" s="22" t="inlineStr">
+      <c r="B31" s="23" t="inlineStr">
         <is>
           <t>A | 744呎 (3房)
 $2306万
@@ -40925,7 +40925,7 @@
 (26年-05月-08日)</t>
         </is>
       </c>
-      <c r="C31" s="22" t="inlineStr">
+      <c r="C31" s="23" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
 $1951万

--- a/九龙-启德-维港．湾畔第2B期/维港．湾畔第2B期_销控明细表.xlsx
+++ b/九龙-启德-维港．湾畔第2B期/维港．湾畔第2B期_销控明细表.xlsx
@@ -27398,23 +27398,19 @@
       </c>
       <c r="F384" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H384" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I384" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H384" s="5" t="n">
+        <v>24146000</v>
+      </c>
+      <c r="I384" s="5" t="n">
+        <v>36201</v>
       </c>
       <c r="J384" s="3" t="inlineStr">
         <is>
@@ -27423,12 +27419,12 @@
       </c>
       <c r="K384" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L384" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M384" s="3" t="inlineStr">
@@ -27438,7 +27434,7 @@
       </c>
       <c r="N384" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -28024,23 +28020,19 @@
       </c>
       <c r="F393" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H393" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I393" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H393" s="5" t="n">
+        <v>24026000</v>
+      </c>
+      <c r="I393" s="5" t="n">
+        <v>36021</v>
       </c>
       <c r="J393" s="3" t="inlineStr">
         <is>
@@ -28049,12 +28041,12 @@
       </c>
       <c r="K393" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L393" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M393" s="3" t="inlineStr">
@@ -28064,7 +28056,7 @@
       </c>
       <c r="N393" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -35501,7 +35493,7 @@
       </c>
       <c r="G501" s="3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="H501" s="5" t="n">
@@ -38809,7 +38801,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -38819,7 +38811,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>39</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -39819,12 +39811,12 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
-招标单位
--
-(在售)</t>
+$2415万
+$36,201/呎
+(26年-08月-12日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -39898,12 +39890,12 @@
 (26年-06月-01日)</t>
         </is>
       </c>
-      <c r="C18" s="22" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
-招标单位
--
-(在售)</t>
+$2403万
+$36,021/呎
+(26年-08月-12日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -40851,7 +40843,7 @@
           <t>B | 667呎 (3房)
 $2151万
 $32,252/呎
-(26年-07月-21日)</t>
+(26年-08月-13日)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">

--- a/九龙-启德-维港．湾畔第2B期/维港．湾畔第2B期_销控明细表.xlsx
+++ b/九龙-启德-维港．湾畔第2B期/维港．湾畔第2B期_销控明细表.xlsx
@@ -31625,7 +31625,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="H445" s="5" t="n">
@@ -40385,7 +40385,7 @@
           <t>D | 662呎 (3房)
 $1909万
 $28,841/呎
-(26年-07月-31日)</t>
+(26年-08月-19日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">

--- a/九龙-启德-维港．湾畔第2B期/维港．湾畔第2B期_销控明细表.xlsx
+++ b/九龙-启德-维港．湾畔第2B期/维港．湾畔第2B期_销控明细表.xlsx
@@ -24770,7 +24770,7 @@
       </c>
       <c r="F346" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G346" s="3" t="inlineStr">
@@ -24780,12 +24780,12 @@
       </c>
       <c r="H346" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I346" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J346" s="3" t="inlineStr">
@@ -24795,12 +24795,12 @@
       </c>
       <c r="K346" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L346" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M346" s="3" t="inlineStr">
@@ -24810,7 +24810,7 @@
       </c>
       <c r="N346" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -25392,7 +25392,7 @@
       </c>
       <c r="F355" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G355" s="3" t="inlineStr">
@@ -25402,12 +25402,12 @@
       </c>
       <c r="H355" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I355" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J355" s="3" t="inlineStr">
@@ -25417,12 +25417,12 @@
       </c>
       <c r="K355" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L355" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M355" s="3" t="inlineStr">
@@ -25432,7 +25432,7 @@
       </c>
       <c r="N355" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -29124,7 +29124,7 @@
       </c>
       <c r="F409" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G409" s="3" t="inlineStr">
@@ -29134,12 +29134,12 @@
       </c>
       <c r="H409" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I409" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J409" s="3" t="inlineStr">
@@ -29149,12 +29149,12 @@
       </c>
       <c r="K409" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L409" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M409" s="3" t="inlineStr">
@@ -29164,7 +29164,7 @@
       </c>
       <c r="N409" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -30376,7 +30376,7 @@
       </c>
       <c r="F427" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G427" s="3" t="inlineStr">
@@ -30386,12 +30386,12 @@
       </c>
       <c r="H427" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I427" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J427" s="3" t="inlineStr">
@@ -30401,12 +30401,12 @@
       </c>
       <c r="K427" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L427" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M427" s="3" t="inlineStr">
@@ -30416,7 +30416,7 @@
       </c>
       <c r="N427" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -30998,23 +30998,19 @@
       </c>
       <c r="F436" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H436" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I436" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="H436" s="5" t="n">
+        <v>19189000</v>
+      </c>
+      <c r="I436" s="5" t="n">
+        <v>28986</v>
       </c>
       <c r="J436" s="3" t="inlineStr">
         <is>
@@ -31023,12 +31019,12 @@
       </c>
       <c r="K436" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L436" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M436" s="3" t="inlineStr">
@@ -31038,7 +31034,7 @@
       </c>
       <c r="N436" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -35348,7 +35344,7 @@
       </c>
       <c r="F499" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G499" s="3" t="inlineStr">
@@ -35358,12 +35354,12 @@
       </c>
       <c r="H499" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I499" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J499" s="3" t="inlineStr">
@@ -35373,12 +35369,12 @@
       </c>
       <c r="K499" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L499" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M499" s="3" t="inlineStr">
@@ -35388,7 +35384,7 @@
       </c>
       <c r="N499" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -35970,7 +35966,7 @@
       </c>
       <c r="F508" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G508" s="3" t="inlineStr">
@@ -35980,12 +35976,12 @@
       </c>
       <c r="H508" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I508" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J508" s="3" t="inlineStr">
@@ -35995,12 +35991,12 @@
       </c>
       <c r="K508" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L508" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M508" s="3" t="inlineStr">
@@ -36010,7 +36006,7 @@
       </c>
       <c r="N508" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -38801,7 +38797,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -38811,7 +38807,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -38821,7 +38817,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>185</t>
         </is>
       </c>
     </row>
@@ -39511,12 +39507,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E13" s="20" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>D | 662呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -39590,12 +39586,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E14" s="20" t="inlineStr">
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>D | 662呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -40064,12 +40060,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E20" s="20" t="inlineStr">
+      <c r="E20" s="22" t="inlineStr">
         <is>
           <t>D | 662呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -40222,12 +40218,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E22" s="20" t="inlineStr">
+      <c r="E22" s="22" t="inlineStr">
         <is>
           <t>D | 662呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -40301,12 +40297,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E23" s="22" t="inlineStr">
+      <c r="E23" s="23" t="inlineStr">
         <is>
           <t>D | 662呎 (3房)
-招标单位
--
-(在售)</t>
+$1919万
+$28,986/呎
+(26年-08月-31日)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -40854,12 +40850,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E30" s="20" t="inlineStr">
+      <c r="E30" s="22" t="inlineStr">
         <is>
           <t>D | 662呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
@@ -40933,12 +40929,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E31" s="20" t="inlineStr">
+      <c r="E31" s="22" t="inlineStr">
         <is>
           <t>D | 662呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
